--- a/PrimareyGLTest5/DataSheet.xlsx
+++ b/PrimareyGLTest5/DataSheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://libertymutual-my.sharepoint.com/personal/mohammad_talib_libertymutual_com/Documents/Desktop/regression-pack/PrimareyGL/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://libertymutual-my.sharepoint.com/personal/mohammad_talib_libertymutual_com/Documents/Desktop/regression-pack/PrimareyGLTest5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="6_{953F3F11-86FF-482F-A46F-765DF7FFE6A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F881687-3F77-47DC-A22D-58EE687BF398}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="6_{953F3F11-86FF-482F-A46F-765DF7FFE6A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29D8D7C2-EC5E-4D8A-8A85-D8687C0B41D0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="3" xr2:uid="{A2EF6AEE-92DE-49D8-BB60-1A120F6353A4}"/>
   </bookViews>
@@ -2084,7 +2084,7 @@
     <t>9/13/2026</t>
   </si>
   <si>
-    <t>https://n9971008:wm$qY@08@test5-underwritingplatform.grsazr.lmig.com</t>
+    <t>https://n9971008:wm$qY@08@hfstage-underwritingplatform.grsazr.lmig.com</t>
   </si>
 </sst>
 </file>
